--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2399"/>
+  <dimension ref="A1:E2400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65189,6 +65189,33 @@
         </is>
       </c>
     </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E2400" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2400"/>
+  <dimension ref="A1:E2401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65216,6 +65216,33 @@
         </is>
       </c>
     </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
